--- a/FNDE/Centro Oeste/Fornecedores/FNDE_LIMPEZA E HIGIENE.xlsx
+++ b/FNDE/Centro Oeste/Fornecedores/FNDE_LIMPEZA E HIGIENE.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L14"/>
+  <dimension ref="A1:L29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1249,6 +1249,756 @@
       <c r="L14" s="2" t="inlineStr">
         <is>
           <t>Empresas_Pesquisa_SEAD_GO_Limpeza_1.xlsx (aba Preço aberto no site)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>CAUE SUPRIMENTOS COMERCIO E SERVICOS LTDA (Cauê Distribuidora)</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>34.853.905/0001-26</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>4649-4/08 (principal); 4649-4/02 (secundário); 4686-9/02 (secundário)</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>https://www.distribuidoracaue.com.br</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>https://www.distribuidoracaue.com.br</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="n"/>
+      <c r="I15" s="2" t="n"/>
+      <c r="J15" s="2" t="n"/>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>Incluído em 13/10/2026 a partir da entrega do William; razão social, UF, cidade e CNAE conferidos na Receita (publica.cnpj.ws). Demais campos não verificados.</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.distribuidoracaue.com.br | https://publica.cnpj.ws/cnpj/34853905000126</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>HYGIE SYSTEMS COMERCIAL E DISTRIBUIDORA LTDA (Melhoramentos Higiene)</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>01.517.623/0001-07</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>4618-4/99 (secundário); 4646-0/01 (secundário); 4649-4/01 (secundário); 4649-4/08 (secundário)</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>https://melhoramentoshigiene.com.br</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>https://melhoramentoshigiene.com.br</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="n"/>
+      <c r="I16" s="2" t="n"/>
+      <c r="J16" s="2" t="n"/>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>Incluído em 13/10/2026 a partir da entrega do William; razão social, UF, cidade e CNAE conferidos na Receita (publica.cnpj.ws). Demais campos não verificados.</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>https://melhoramentoshigiene.com.br | https://publica.cnpj.ws/cnpj/01517623000107</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Santo Antônio de Posse</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>INSTITUTO DA LIMPEZA COMERCIO E SERVICOS LTDA (General Clean)</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>17.587.390/0001-40</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>4649-4/08 (principal); 4645-1/01 (secundário); 4646-0/01 (secundário); 4646-0/02 (secundário)</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>https://www.generalclean.com.br</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>https://www.generalclean.com.br</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="n"/>
+      <c r="I17" s="2" t="n"/>
+      <c r="J17" s="2" t="n"/>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>Incluído em 13/10/2026 a partir da entrega do William; razão social, UF, cidade e CNAE conferidos na Receita (publica.cnpj.ws). Demais campos não verificados.</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.generalclean.com.br | https://publica.cnpj.ws/cnpj/17587390000140</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Guarulhos</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>GUARULHOS DISTRIBUIDORA DE EMBALAGENS LTDA (Guarulhos Embalagens)</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>30.679.614/0001-02</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>4686-9/02 (principal); 4647-8/01 (secundário); 4649-4/08 (secundário); 4649-4/99 (secundário); 4689-3/99 (secundário)</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>https://www.guarulhosembalagens.com.br</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>https://www.guarulhosembalagens.com.br</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="n"/>
+      <c r="I18" s="2" t="n"/>
+      <c r="J18" s="2" t="n"/>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>Incluído em 13/10/2026 a partir da entrega do William; razão social, UF, cidade e CNAE conferidos na Receita (publica.cnpj.ws). Demais campos não verificados.</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.guarulhosembalagens.com.br | https://publica.cnpj.ws/cnpj/30679614000102</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Flores da Cunha</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>CASA DOS QUIMICOS COMERCIO DE PRODUTOS QUIMICOS LTDA (Casa dos Químicos)</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>30.799.772/0001-04</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>4684-2/99 (principal)</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>https://www.casadosquimicos.com.br</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>https://www.casadosquimicos.com.br</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="n"/>
+      <c r="I19" s="2" t="n"/>
+      <c r="J19" s="2" t="n"/>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>Incluído em 13/10/2026 a partir da entrega do William; razão social, UF, cidade e CNAE conferidos na Receita (publica.cnpj.ws). Demais campos não verificados.</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>https://www.casadosquimicos.com.br | https://publica.cnpj.ws/cnpj/30799772000104</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Santo André</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>NOVA LIMP COMERCIO DE EMBALAGENS E DESCARTAVEIS LTDA (Nova Limp)</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>04.681.311/0001-14</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>4693-1/00 (principal); 4649-4/99 (secundário); 4686-9/02 (secundário)</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>https://www.novalimp.com.br</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>https://www.novalimp.com.br</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="n"/>
+      <c r="I20" s="2" t="n"/>
+      <c r="J20" s="2" t="n"/>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>Incluído em 13/10/2026 a partir da entrega do William; razão social, UF, cidade e CNAE conferidos na Receita (publica.cnpj.ws). Demais campos não verificados.</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>https://www.novalimp.com.br | https://publica.cnpj.ws/cnpj/04681311000114</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Montes Claros</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>NOVO AROMA COMERCIO DE PRODUTOS DE LIMPEZA &amp; HIGIENE LTDA (Shopping da Limpeza)</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>07.904.575/0001-88</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>4635-4/99 (secundário); 4641-9/02 (secundário); 4641-9/03 (secundário); 4646-0/01 (secundário); 4647-8/01 (secundário); 4649-4/02 (secundário); 4649-4/04 (secundário); 4649-4/08 (secundário); 4649-4/99 (secundário); 4651-6/01 (secundário); 4651-6/02 (secundário); 4663-0/00 (secundário); 4672-9/00 (secundário); 4691-5/00 (secundário)</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>https://www.shoppingdalimpeza.com</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>https://www.shoppingdalimpeza.com</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="n"/>
+      <c r="I21" s="2" t="n"/>
+      <c r="J21" s="2" t="n"/>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>Incluído em 13/10/2026 a partir da entrega do William; razão social, UF, cidade e CNAE conferidos na Receita (publica.cnpj.ws). Demais campos não verificados.</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>https://www.shoppingdalimpeza.com | https://publica.cnpj.ws/cnpj/07904575000188</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>SHOP PROFISSIONAL DA LIMPEZA E VARIEDADES LTDA (Profissional da Limpeza)</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>45.343.703/0001-50</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>4649-4/08 (principal)</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>https://profissionaldalimpeza.commercesuite.com.br</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>https://profissionaldalimpeza.commercesuite.com.br</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="n"/>
+      <c r="I22" s="2" t="n"/>
+      <c r="J22" s="2" t="n"/>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>Incluído em 13/10/2026 a partir da entrega do William; razão social, UF, cidade e CNAE conferidos na Receita (publica.cnpj.ws). Demais campos não verificados.</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>https://profissionaldalimpeza.commercesuite.com.br | https://publica.cnpj.ws/cnpj/45343703000150</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Ijuí</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>H D DISTRIBUIDORA DE PRODUTOS HIGIENICOS E DESCARTAVEIS LTDA (HD Distribuidora)</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>03.868.183/0001-50</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>4637-1/01 (secundário); 4637-1/02 (secundário); 4646-0/01 (secundário); 4649-4/08 (secundário)</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>https://hddistribuidora.com</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>https://hddistribuidora.com</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="n"/>
+      <c r="I23" s="2" t="n"/>
+      <c r="J23" s="2" t="n"/>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>Incluído em 13/10/2026 a partir da entrega do William; razão social, UF, cidade e CNAE conferidos na Receita (publica.cnpj.ws). Demais campos não verificados.</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>https://hddistribuidora.com | https://publica.cnpj.ws/cnpj/03868183000150</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Franca</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>PALACIO DAS FERRAMENTAS E PARAFUSOS LTDA (Palácio das Ferramentas)</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>68.422.419/0001-75</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>4661-3/00 (secundário); 4662-1/00 (secundário); 4663-0/00 (secundário); 4672-9/00 (secundário)</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>https://palaciodasferramentas.com.br</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>https://palaciodasferramentas.com.br</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="n"/>
+      <c r="I24" s="2" t="n"/>
+      <c r="J24" s="2" t="n"/>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>Incluído em 13/10/2026 a partir da entrega do William; razão social, UF, cidade e CNAE conferidos na Receita (publica.cnpj.ws). Demais campos não verificados.</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>https://palaciodasferramentas.com.br | https://publica.cnpj.ws/cnpj/68422419000175</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Rolante</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>HIGIENIZE COMERCIAL LTDA (Higienize)</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>95.054.177/0001-87</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>4649-4/08 (principal); 4642-7/02 (secundário); 4646-0/01 (secundário); 4646-0/02 (secundário); 4647-8/01 (secundário); 4649-4/01 (secundário); 4649-4/05 (secundário); 4649-4/99 (secundário); 4663-0/00 (secundário); 4669-9/99 (secundário); 4684-2/99 (secundário); 4686-9/02 (secundário)</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>https://www.higienize.com</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>https://www.higienize.com</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="n"/>
+      <c r="I25" s="2" t="n"/>
+      <c r="J25" s="2" t="n"/>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>Incluído em 13/10/2026 a partir da entrega do William; razão social, UF, cidade e CNAE conferidos na Receita (publica.cnpj.ws). Demais campos não verificados.</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>https://www.higienize.com | https://publica.cnpj.ws/cnpj/95054177000187</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Dois Irmãos</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>LF COMERCIAL DE BENS LTDA (LF Máquinas e Ferramentas)</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>91.845.735/0004-14</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>4672-9/00 (principal); 4641-9/02 (secundário); 4642-7/02 (secundário); 4649-4/02 (secundário); 4649-4/03 (secundário); 4649-4/04 (secundário); 4649-4/08 (secundário); 4649-4/99 (secundário); 4651-6/01 (secundário); 4651-6/02 (secundário); 4652-4/00 (secundário); 4661-3/00 (secundário); 4669-9/99 (secundário); 4671-1/00 (secundário); 4679-6/01 (secundário); 4679-6/04 (secundário); 4679-6/99 (secundário)</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>https://www.lfmaquinaseferramentas.com.br</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>https://www.lfmaquinaseferramentas.com.br</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="n"/>
+      <c r="I26" s="2" t="n"/>
+      <c r="J26" s="2" t="n"/>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>Incluído em 13/10/2026 a partir da entrega do William; razão social, UF, cidade e CNAE conferidos na Receita (publica.cnpj.ws). Demais campos não verificados.</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>https://www.lfmaquinaseferramentas.com.br | https://publica.cnpj.ws/cnpj/91845735000414</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Chapecó</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>PREVEOESTE MATERIAIS DE SEGURANCA E DESCARTAVEIS LTDA (PreveOeste)</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>01.974.824/0001-25</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>4642-7/02 (principal); 4649-4/99 (secundário); 4686-9/02 (secundário)</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>https://www.preveoeste.com.br</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>https://www.preveoeste.com.br</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="n"/>
+      <c r="I27" s="2" t="n"/>
+      <c r="J27" s="2" t="n"/>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>Incluído em 13/10/2026 a partir da entrega do William; razão social, UF, cidade e CNAE conferidos na Receita (publica.cnpj.ws). Demais campos não verificados.</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>https://www.preveoeste.com.br | https://publica.cnpj.ws/cnpj/01974824000125</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>VW COMERCIO DE HIDRAULICA E PLASTICOS INDUSTRIAIS LTDA (Plásticos Ipiranga)</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>19.218.815/0001-70</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>4686-9/02 (principal); 4642-7/02 (secundário); 4649-4/04 (secundário)</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>https://loja.plasticosipiranga.com.br</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>https://loja.plasticosipiranga.com.br</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="n"/>
+      <c r="I28" s="2" t="n"/>
+      <c r="J28" s="2" t="n"/>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>Incluído em 13/10/2026 a partir da entrega do William; razão social, UF, cidade e CNAE conferidos na Receita (publica.cnpj.ws). Demais campos não verificados.</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>https://loja.plasticosipiranga.com.br | https://publica.cnpj.ws/cnpj/19218815000170</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Braço do Norte</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>ATACADO VENCEDOR LTDA (Atacado Vencedor)</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>43.489.766/0001-94</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>4693-1/00 (principal); 4641-9/02 (secundário); 4642-7/01 (secundário); 4649-4/99 (secundário)</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>https://www.atacadovencedor.com</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>https://www.atacadovencedor.com</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="n"/>
+      <c r="I29" s="2" t="n"/>
+      <c r="J29" s="2" t="n"/>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>Incluído em 13/10/2026 a partir da entrega do William; razão social, UF, cidade e CNAE conferidos na Receita (publica.cnpj.ws). Demais campos não verificados.</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>https://www.atacadovencedor.com | https://publica.cnpj.ws/cnpj/43489766000194</t>
         </is>
       </c>
     </row>
@@ -1290,6 +2040,21 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G13" r:id="rId33"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F14" r:id="rId34"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G14" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G15" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G16" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G17" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G18" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G19" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G20" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G21" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G22" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G23" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G24" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G25" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G26" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G27" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G28" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G29" r:id="rId50"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3108,7 +3873,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
@@ -3190,7 +3954,6 @@
         </is>
       </c>
     </row>
-    <row r="7"/>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
